--- a/ClosedXML.Tests/Resource/Examples/Ranges/SortExample.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/SortExample.xlsx
@@ -810,11 +810,11 @@
       <x:c r="H5" s="9" t="s"/>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="A8" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>5</x:v>
+      <x:c r="A8" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
         <x:v>5</x:v>
@@ -834,11 +834,11 @@
       <x:c r="H8" s="8" t="s"/>
     </x:row>
     <x:row r="9" spans="1:8">
-      <x:c r="A9" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>5</x:v>
+      <x:c r="A9" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
         <x:v>5</x:v>
@@ -858,11 +858,11 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:8">
-      <x:c r="A10" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="s">
-        <x:v>7</x:v>
+      <x:c r="A10" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
         <x:v>6</x:v>
@@ -938,13 +938,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s"/>
-      <x:c r="F6" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G6" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="7" t="s">
+      <x:c r="F6" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -958,13 +958,13 @@
       <x:c r="C7" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H7" s="6" t="s">
+      <x:c r="F7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G7" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1300,13 +1300,13 @@
       <x:c r="A9" s="7" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="s"/>
+      <x:c r="D9" s="5" t="s"/>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="5" t="s"/>
+      <x:c r="D10" s="8" t="s"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1341,14 +1341,14 @@
       <x:c r="C3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>5</x:v>
+      <x:c r="F3" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
@@ -1359,14 +1359,14 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s"/>
-      <x:c r="F4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G4" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="s">
-        <x:v>7</x:v>
+      <x:c r="F4" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
